--- a/inquiry_forms/022_packaging_innovation_inquiry_contact_form--inquiry_forms.xlsx
+++ b/inquiry_forms/022_packaging_innovation_inquiry_contact_form--inquiry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'project_brief'}</t>
+          <t>project_brief</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Project Brief'}</t>
+          <t>Project Brief</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'innovation_inquiry'}</t>
+          <t>innovation_inquiry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Innovation Inquiry'}</t>
+          <t>Innovation Inquiry</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'collaboration_request'}</t>
+          <t>collaboration_request</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Collaboration Request'}</t>
+          <t>Collaboration Request</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'partnership'}</t>
+          <t>partnership</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Partnership'}</t>
+          <t>Partnership</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'joint_development'}</t>
+          <t>joint_development</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Joint Development'}</t>
+          <t>Joint Development</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'In-Person'}</t>
+          <t>In-Person</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'food_and_beverage'}</t>
+          <t>food_and_beverage</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Food and Beverage'}</t>
+          <t>Food and Beverage</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'personal_care'}</t>
+          <t>personal_care</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Personal Care'}</t>
+          <t>Personal Care</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'pharmaceutical'}</t>
+          <t>pharmaceutical</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Pharmaceutical'}</t>
+          <t>Pharmaceutical</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'cosmetic'}</t>
+          <t>cosmetic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Cosmetic'}</t>
+          <t>Cosmetic</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'health_&amp;_wellness'}</t>
+          <t>health_&amp;_wellness</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Health &amp; Wellness'}</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
